--- a/data/Heat map 4-1 Research Outputs.xlsx
+++ b/data/Heat map 4-1 Research Outputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F193B06-0BBE-4715-A1DE-52D5A03CCCB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF81C91C-1596-48F9-B57F-1868243F0A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{60C6FB9E-1B92-4818-B8F8-C10D82D4AFAC}"/>
   </bookViews>
@@ -557,19 +557,10 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -579,8 +570,89 @@
     <xf numFmtId="1" fontId="2" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -600,15 +672,18 @@
     <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -618,110 +693,32 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1027,616 +1024,734 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B183A326-557F-46A5-AEA8-D42BBCF0052C}">
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.21875" customWidth="1"/>
     <col min="2" max="2" width="30.88671875" customWidth="1"/>
-    <col min="3" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="8.88671875" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="2" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C1" s="13" t="s">
+    <row r="1" spans="1:23" s="2" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C1" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="15"/>
-    </row>
-    <row r="2" spans="1:20" s="1" customFormat="1" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22"/>
-      <c r="B2" s="32" t="s">
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+    </row>
+    <row r="2" spans="1:23" s="1" customFormat="1" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="49"/>
+      <c r="B2" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="16" t="s">
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="16" t="s">
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="17"/>
-      <c r="T2" s="18"/>
-    </row>
-    <row r="3" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="22"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="30" t="s">
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="41"/>
+      <c r="T2" s="42"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+    </row>
+    <row r="3" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="49"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="Q3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="R3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="S3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="T3" s="8" t="s">
+      <c r="T3" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+    </row>
+    <row r="4" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="50">
         <v>21.95</v>
       </c>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="9">
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="50">
         <v>3.1357142857142857</v>
       </c>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="9">
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="50">
         <v>1</v>
       </c>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="51"/>
-    </row>
-    <row r="5" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="20"/>
-      <c r="B5" s="24" t="s">
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="30"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+    </row>
+    <row r="5" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="45"/>
+      <c r="B5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="52">
+      <c r="C5" s="51">
         <v>51.45</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="52">
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="51">
         <v>2.2369565217391307</v>
       </c>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="53"/>
-      <c r="O5" s="52">
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="51">
         <v>0</v>
       </c>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="53"/>
-    </row>
-    <row r="6" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="20"/>
-      <c r="B6" s="24" t="s">
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="30"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="30"/>
+    </row>
+    <row r="6" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="45"/>
+      <c r="B6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="52">
+      <c r="C6" s="51">
         <v>5</v>
       </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="52">
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="51">
         <v>1.25</v>
       </c>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="53"/>
-      <c r="O6" s="52">
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="51">
         <v>0</v>
       </c>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="28"/>
-      <c r="T6" s="53"/>
-    </row>
-    <row r="7" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="21"/>
-      <c r="B7" s="25" t="s">
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
+      <c r="T6" s="27"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="30"/>
+    </row>
+    <row r="7" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="46"/>
+      <c r="B7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="52">
+      <c r="C7" s="51">
         <v>15.4</v>
       </c>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="52">
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="51">
         <v>1.0266666666666666</v>
       </c>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="53"/>
-      <c r="O7" s="52">
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="51">
         <v>0</v>
       </c>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28"/>
-      <c r="T7" s="53"/>
-    </row>
-    <row r="8" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="30"/>
+    </row>
+    <row r="8" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="52">
+      <c r="C8" s="51">
         <v>41.45</v>
       </c>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="52">
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="51">
         <v>3.4541666666666671</v>
       </c>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="53"/>
-      <c r="O8" s="52">
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="51">
         <v>1</v>
       </c>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="28"/>
-      <c r="S8" s="28"/>
-      <c r="T8" s="53"/>
-    </row>
-    <row r="9" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="20"/>
-      <c r="B9" s="24" t="s">
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="30"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="30"/>
+    </row>
+    <row r="9" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="45"/>
+      <c r="B9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="52">
+      <c r="C9" s="51">
         <v>20.87</v>
       </c>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="52">
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="51">
         <v>1.0435000000000001</v>
       </c>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="52">
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="51">
         <v>1</v>
       </c>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="28"/>
-      <c r="T9" s="53"/>
-    </row>
-    <row r="10" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20"/>
-      <c r="B10" s="24" t="s">
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
+      <c r="T9" s="27"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="30"/>
+    </row>
+    <row r="10" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="45"/>
+      <c r="B10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="52">
+      <c r="C10" s="51">
         <v>15.5</v>
       </c>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="52">
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="51">
         <v>2.2142857142857144</v>
       </c>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-      <c r="M10" s="28"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="52">
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="51">
         <v>2</v>
       </c>
-      <c r="P10" s="28"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="28"/>
-      <c r="S10" s="28"/>
-      <c r="T10" s="53"/>
-    </row>
-    <row r="11" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="21"/>
-      <c r="B11" s="26" t="s">
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="30"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="30"/>
+    </row>
+    <row r="11" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="46"/>
+      <c r="B11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="52">
+      <c r="C11" s="51">
         <v>0</v>
       </c>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="52">
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="51">
         <v>0</v>
       </c>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="28"/>
-      <c r="M11" s="28"/>
-      <c r="N11" s="53"/>
-      <c r="O11" s="52">
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="51">
         <v>0</v>
       </c>
-      <c r="P11" s="28"/>
-      <c r="Q11" s="28"/>
-      <c r="R11" s="28"/>
-      <c r="S11" s="28"/>
-      <c r="T11" s="53"/>
-    </row>
-    <row r="12" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="27"/>
+      <c r="U11" s="30"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="30"/>
+    </row>
+    <row r="12" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="52">
+      <c r="C12" s="51">
         <v>9.92</v>
       </c>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="52">
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="51">
         <v>0.90181818181818185</v>
       </c>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-      <c r="M12" s="28"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="52">
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="51">
         <v>0</v>
       </c>
-      <c r="P12" s="28"/>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="28"/>
-      <c r="S12" s="28"/>
-      <c r="T12" s="53"/>
-    </row>
-    <row r="13" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="24" t="s">
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="27"/>
+      <c r="U12" s="30"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="30"/>
+    </row>
+    <row r="13" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="35"/>
+      <c r="B13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="52">
+      <c r="C13" s="51">
         <v>6.6</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="52">
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="51">
         <v>0.6</v>
       </c>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="52">
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="51">
         <v>0</v>
       </c>
-      <c r="P13" s="28"/>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="28"/>
-      <c r="S13" s="28"/>
-      <c r="T13" s="53"/>
-    </row>
-    <row r="14" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="24" t="s">
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="27"/>
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="30"/>
+    </row>
+    <row r="14" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="35"/>
+      <c r="B14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="52">
+      <c r="C14" s="51">
         <v>13.33</v>
       </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="52">
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="51">
         <v>2.6659999999999999</v>
       </c>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="28"/>
-      <c r="M14" s="28"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="52">
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="51">
         <v>1</v>
       </c>
-      <c r="P14" s="28"/>
-      <c r="Q14" s="28"/>
-      <c r="R14" s="28"/>
-      <c r="S14" s="28"/>
-      <c r="T14" s="53"/>
-    </row>
-    <row r="15" spans="1:20" s="1" customFormat="1" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="24" t="s">
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="27"/>
+      <c r="U14" s="30"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="30"/>
+    </row>
+    <row r="15" spans="1:23" s="1" customFormat="1" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="35"/>
+      <c r="B15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="52">
+      <c r="C15" s="51">
         <v>12.5</v>
       </c>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="52">
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="51">
         <v>3.125</v>
       </c>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-      <c r="M15" s="28"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="52">
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="51">
         <v>0</v>
       </c>
-      <c r="P15" s="28"/>
-      <c r="Q15" s="28"/>
-      <c r="R15" s="28"/>
-      <c r="S15" s="28"/>
-      <c r="T15" s="53"/>
-    </row>
-    <row r="16" spans="1:20" s="2" customFormat="1" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="12"/>
-      <c r="B16" s="27" t="s">
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="30"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="30"/>
+    </row>
+    <row r="16" spans="1:23" s="2" customFormat="1" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="36"/>
+      <c r="B16" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="54">
+      <c r="C16" s="52">
         <v>3</v>
       </c>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="54">
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="52">
         <v>0.3</v>
       </c>
-      <c r="J16" s="55"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="55"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="54">
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="52">
         <v>0</v>
       </c>
-      <c r="P16" s="55"/>
-      <c r="Q16" s="55"/>
-      <c r="R16" s="55"/>
-      <c r="S16" s="55"/>
-      <c r="T16" s="56"/>
-    </row>
-    <row r="17" spans="1:20" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="30"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="30"/>
+    </row>
+    <row r="17" spans="1:23" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="33"/>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="53">
         <v>272</v>
       </c>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="42">
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="19">
         <v>2</v>
       </c>
-      <c r="J17" s="41"/>
-      <c r="K17" s="41"/>
-      <c r="L17" s="41"/>
-      <c r="M17" s="41"/>
-      <c r="N17" s="41"/>
-      <c r="O17" s="43">
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="19">
         <v>13</v>
       </c>
-      <c r="P17" s="41"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="41"/>
-      <c r="S17" s="41"/>
-      <c r="T17" s="44"/>
-    </row>
-    <row r="18" spans="1:20" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="34"/>
-      <c r="B18" s="36" t="s">
+      <c r="P17" s="18"/>
+      <c r="Q17" s="18"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="18"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="30"/>
+      <c r="V17" s="30"/>
+      <c r="W17" s="30"/>
+    </row>
+    <row r="18" spans="1:23" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="30"/>
+      <c r="B18" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="54">
         <v>216.97</v>
       </c>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="39">
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="17">
         <v>1.6887775412992805</v>
       </c>
-      <c r="J18" s="38"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="40">
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="17">
         <v>6</v>
       </c>
-      <c r="P18" s="38"/>
-      <c r="Q18" s="38"/>
-      <c r="R18" s="38"/>
-      <c r="S18" s="38"/>
-      <c r="T18" s="45"/>
-    </row>
-    <row r="19" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="34"/>
-      <c r="B19" s="37" t="s">
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="16"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="30"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="30"/>
+    </row>
+    <row r="19" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="30"/>
+      <c r="B19" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="55">
         <v>20.923076923076923</v>
       </c>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="47">
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="23">
         <v>2</v>
       </c>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="46"/>
-      <c r="O19" s="48">
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="23">
         <v>1</v>
       </c>
-      <c r="P19" s="46"/>
-      <c r="Q19" s="46"/>
-      <c r="R19" s="46"/>
-      <c r="S19" s="46"/>
-      <c r="T19" s="49"/>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A20" s="34"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22"/>
+      <c r="R19" s="22"/>
+      <c r="S19" s="22"/>
+      <c r="T19" s="24"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A20" s="30"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A21" s="30"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A22" s="30"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="32"/>
+      <c r="P22" s="32"/>
+      <c r="Q22" s="32"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A17:A20"/>
+  <mergeCells count="12">
+    <mergeCell ref="U1:W1048576"/>
+    <mergeCell ref="B20:S22"/>
+    <mergeCell ref="A17:A22"/>
     <mergeCell ref="A12:A16"/>
     <mergeCell ref="C1:T1"/>
     <mergeCell ref="C2:H2"/>

--- a/data/Heat map 4-1 Research Outputs.xlsx
+++ b/data/Heat map 4-1 Research Outputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF81C91C-1596-48F9-B57F-1868243F0A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476F243A-8224-4B69-8902-641E49D24F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{60C6FB9E-1B92-4818-B8F8-C10D82D4AFAC}"/>
   </bookViews>
@@ -642,6 +642,24 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -701,24 +719,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1031,70 +1031,70 @@
     <col min="2" max="2" width="30.88671875" customWidth="1"/>
     <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="8.88671875" style="30"/>
+    <col min="21" max="23" width="8.88671875" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="2" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
     </row>
     <row r="2" spans="1:23" s="1" customFormat="1" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="49"/>
-      <c r="B2" s="47" t="s">
+      <c r="A2" s="55"/>
+      <c r="B2" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43" t="s">
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="43" t="s">
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
     </row>
     <row r="3" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="49"/>
-      <c r="B3" s="48"/>
+      <c r="A3" s="55"/>
+      <c r="B3" s="54"/>
       <c r="C3" s="12" t="s">
         <v>0</v>
       </c>
@@ -1149,18 +1149,18 @@
       <c r="T3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="30"/>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="36"/>
     </row>
     <row r="4" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="50" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="50">
+      <c r="C4" s="30">
         <v>21.95</v>
       </c>
       <c r="D4" s="25"/>
@@ -1168,7 +1168,7 @@
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
       <c r="H4" s="26"/>
-      <c r="I4" s="50">
+      <c r="I4" s="30">
         <v>3.1357142857142857</v>
       </c>
       <c r="J4" s="25"/>
@@ -1176,7 +1176,7 @@
       <c r="L4" s="25"/>
       <c r="M4" s="25"/>
       <c r="N4" s="26"/>
-      <c r="O4" s="50">
+      <c r="O4" s="30">
         <v>1</v>
       </c>
       <c r="P4" s="25"/>
@@ -1184,16 +1184,16 @@
       <c r="R4" s="25"/>
       <c r="S4" s="25"/>
       <c r="T4" s="26"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
     </row>
     <row r="5" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="45"/>
+      <c r="A5" s="51"/>
       <c r="B5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="51">
+      <c r="C5" s="31">
         <v>51.45</v>
       </c>
       <c r="D5" s="11"/>
@@ -1201,7 +1201,7 @@
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="27"/>
-      <c r="I5" s="51">
+      <c r="I5" s="31">
         <v>2.2369565217391307</v>
       </c>
       <c r="J5" s="11"/>
@@ -1209,7 +1209,7 @@
       <c r="L5" s="11"/>
       <c r="M5" s="11"/>
       <c r="N5" s="27"/>
-      <c r="O5" s="51">
+      <c r="O5" s="31">
         <v>0</v>
       </c>
       <c r="P5" s="11"/>
@@ -1217,16 +1217,16 @@
       <c r="R5" s="11"/>
       <c r="S5" s="11"/>
       <c r="T5" s="27"/>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
+      <c r="U5" s="36"/>
+      <c r="V5" s="36"/>
+      <c r="W5" s="36"/>
     </row>
     <row r="6" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="45"/>
+      <c r="A6" s="51"/>
       <c r="B6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="51">
+      <c r="C6" s="31">
         <v>5</v>
       </c>
       <c r="D6" s="11"/>
@@ -1234,7 +1234,7 @@
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="27"/>
-      <c r="I6" s="51">
+      <c r="I6" s="31">
         <v>1.25</v>
       </c>
       <c r="J6" s="11"/>
@@ -1242,7 +1242,7 @@
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
       <c r="N6" s="27"/>
-      <c r="O6" s="51">
+      <c r="O6" s="31">
         <v>0</v>
       </c>
       <c r="P6" s="11"/>
@@ -1250,16 +1250,16 @@
       <c r="R6" s="11"/>
       <c r="S6" s="11"/>
       <c r="T6" s="27"/>
-      <c r="U6" s="30"/>
-      <c r="V6" s="30"/>
-      <c r="W6" s="30"/>
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+      <c r="W6" s="36"/>
     </row>
     <row r="7" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="46"/>
+      <c r="A7" s="52"/>
       <c r="B7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="51">
+      <c r="C7" s="31">
         <v>15.4</v>
       </c>
       <c r="D7" s="11"/>
@@ -1267,7 +1267,7 @@
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="27"/>
-      <c r="I7" s="51">
+      <c r="I7" s="31">
         <v>1.0266666666666666</v>
       </c>
       <c r="J7" s="11"/>
@@ -1275,7 +1275,7 @@
       <c r="L7" s="11"/>
       <c r="M7" s="11"/>
       <c r="N7" s="27"/>
-      <c r="O7" s="51">
+      <c r="O7" s="31">
         <v>0</v>
       </c>
       <c r="P7" s="11"/>
@@ -1283,18 +1283,18 @@
       <c r="R7" s="11"/>
       <c r="S7" s="11"/>
       <c r="T7" s="27"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
+      <c r="U7" s="36"/>
+      <c r="V7" s="36"/>
+      <c r="W7" s="36"/>
     </row>
     <row r="8" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="50" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="51">
+      <c r="C8" s="31">
         <v>41.45</v>
       </c>
       <c r="D8" s="11"/>
@@ -1302,7 +1302,7 @@
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="27"/>
-      <c r="I8" s="51">
+      <c r="I8" s="31">
         <v>3.4541666666666671</v>
       </c>
       <c r="J8" s="11"/>
@@ -1310,7 +1310,7 @@
       <c r="L8" s="11"/>
       <c r="M8" s="11"/>
       <c r="N8" s="27"/>
-      <c r="O8" s="51">
+      <c r="O8" s="31">
         <v>1</v>
       </c>
       <c r="P8" s="11"/>
@@ -1318,16 +1318,16 @@
       <c r="R8" s="11"/>
       <c r="S8" s="11"/>
       <c r="T8" s="27"/>
-      <c r="U8" s="30"/>
-      <c r="V8" s="30"/>
-      <c r="W8" s="30"/>
+      <c r="U8" s="36"/>
+      <c r="V8" s="36"/>
+      <c r="W8" s="36"/>
     </row>
     <row r="9" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="45"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="51">
+      <c r="C9" s="31">
         <v>20.87</v>
       </c>
       <c r="D9" s="11"/>
@@ -1335,7 +1335,7 @@
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="27"/>
-      <c r="I9" s="51">
+      <c r="I9" s="31">
         <v>1.0435000000000001</v>
       </c>
       <c r="J9" s="11"/>
@@ -1343,7 +1343,7 @@
       <c r="L9" s="11"/>
       <c r="M9" s="11"/>
       <c r="N9" s="27"/>
-      <c r="O9" s="51">
+      <c r="O9" s="31">
         <v>1</v>
       </c>
       <c r="P9" s="11"/>
@@ -1351,16 +1351,16 @@
       <c r="R9" s="11"/>
       <c r="S9" s="11"/>
       <c r="T9" s="27"/>
-      <c r="U9" s="30"/>
-      <c r="V9" s="30"/>
-      <c r="W9" s="30"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="36"/>
+      <c r="W9" s="36"/>
     </row>
     <row r="10" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="51">
+      <c r="C10" s="31">
         <v>15.5</v>
       </c>
       <c r="D10" s="11"/>
@@ -1368,7 +1368,7 @@
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="H10" s="27"/>
-      <c r="I10" s="51">
+      <c r="I10" s="31">
         <v>2.2142857142857144</v>
       </c>
       <c r="J10" s="11"/>
@@ -1376,7 +1376,7 @@
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
       <c r="N10" s="27"/>
-      <c r="O10" s="51">
+      <c r="O10" s="31">
         <v>2</v>
       </c>
       <c r="P10" s="11"/>
@@ -1384,16 +1384,16 @@
       <c r="R10" s="11"/>
       <c r="S10" s="11"/>
       <c r="T10" s="27"/>
-      <c r="U10" s="30"/>
-      <c r="V10" s="30"/>
-      <c r="W10" s="30"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="36"/>
+      <c r="W10" s="36"/>
     </row>
     <row r="11" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="46"/>
+      <c r="A11" s="52"/>
       <c r="B11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="51">
+      <c r="C11" s="31">
         <v>0</v>
       </c>
       <c r="D11" s="11"/>
@@ -1401,7 +1401,7 @@
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="27"/>
-      <c r="I11" s="51">
+      <c r="I11" s="31">
         <v>0</v>
       </c>
       <c r="J11" s="11"/>
@@ -1409,7 +1409,7 @@
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
       <c r="N11" s="27"/>
-      <c r="O11" s="51">
+      <c r="O11" s="31">
         <v>0</v>
       </c>
       <c r="P11" s="11"/>
@@ -1417,18 +1417,18 @@
       <c r="R11" s="11"/>
       <c r="S11" s="11"/>
       <c r="T11" s="27"/>
-      <c r="U11" s="30"/>
-      <c r="V11" s="30"/>
-      <c r="W11" s="30"/>
+      <c r="U11" s="36"/>
+      <c r="V11" s="36"/>
+      <c r="W11" s="36"/>
     </row>
     <row r="12" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="40" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="31">
         <v>9.92</v>
       </c>
       <c r="D12" s="11"/>
@@ -1436,7 +1436,7 @@
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
       <c r="H12" s="27"/>
-      <c r="I12" s="51">
+      <c r="I12" s="31">
         <v>0.90181818181818185</v>
       </c>
       <c r="J12" s="11"/>
@@ -1444,7 +1444,7 @@
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
       <c r="N12" s="27"/>
-      <c r="O12" s="51">
+      <c r="O12" s="31">
         <v>0</v>
       </c>
       <c r="P12" s="11"/>
@@ -1452,16 +1452,16 @@
       <c r="R12" s="11"/>
       <c r="S12" s="11"/>
       <c r="T12" s="27"/>
-      <c r="U12" s="30"/>
-      <c r="V12" s="30"/>
-      <c r="W12" s="30"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="36"/>
+      <c r="W12" s="36"/>
     </row>
     <row r="13" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="35"/>
+      <c r="A13" s="41"/>
       <c r="B13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="51">
+      <c r="C13" s="31">
         <v>6.6</v>
       </c>
       <c r="D13" s="11"/>
@@ -1469,7 +1469,7 @@
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
       <c r="H13" s="27"/>
-      <c r="I13" s="51">
+      <c r="I13" s="31">
         <v>0.6</v>
       </c>
       <c r="J13" s="11"/>
@@ -1477,7 +1477,7 @@
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
       <c r="N13" s="27"/>
-      <c r="O13" s="51">
+      <c r="O13" s="31">
         <v>0</v>
       </c>
       <c r="P13" s="11"/>
@@ -1485,16 +1485,16 @@
       <c r="R13" s="11"/>
       <c r="S13" s="11"/>
       <c r="T13" s="27"/>
-      <c r="U13" s="30"/>
-      <c r="V13" s="30"/>
-      <c r="W13" s="30"/>
+      <c r="U13" s="36"/>
+      <c r="V13" s="36"/>
+      <c r="W13" s="36"/>
     </row>
     <row r="14" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="35"/>
+      <c r="A14" s="41"/>
       <c r="B14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="51">
+      <c r="C14" s="31">
         <v>13.33</v>
       </c>
       <c r="D14" s="11"/>
@@ -1502,7 +1502,7 @@
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
       <c r="H14" s="27"/>
-      <c r="I14" s="51">
+      <c r="I14" s="31">
         <v>2.6659999999999999</v>
       </c>
       <c r="J14" s="11"/>
@@ -1510,7 +1510,7 @@
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
       <c r="N14" s="27"/>
-      <c r="O14" s="51">
+      <c r="O14" s="31">
         <v>1</v>
       </c>
       <c r="P14" s="11"/>
@@ -1518,16 +1518,16 @@
       <c r="R14" s="11"/>
       <c r="S14" s="11"/>
       <c r="T14" s="27"/>
-      <c r="U14" s="30"/>
-      <c r="V14" s="30"/>
-      <c r="W14" s="30"/>
+      <c r="U14" s="36"/>
+      <c r="V14" s="36"/>
+      <c r="W14" s="36"/>
     </row>
     <row r="15" spans="1:23" s="1" customFormat="1" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="35"/>
+      <c r="A15" s="41"/>
       <c r="B15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="51">
+      <c r="C15" s="31">
         <v>12.5</v>
       </c>
       <c r="D15" s="11"/>
@@ -1535,7 +1535,7 @@
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
       <c r="H15" s="27"/>
-      <c r="I15" s="51">
+      <c r="I15" s="31">
         <v>3.125</v>
       </c>
       <c r="J15" s="11"/>
@@ -1543,7 +1543,7 @@
       <c r="L15" s="11"/>
       <c r="M15" s="11"/>
       <c r="N15" s="27"/>
-      <c r="O15" s="51">
+      <c r="O15" s="31">
         <v>0</v>
       </c>
       <c r="P15" s="11"/>
@@ -1551,16 +1551,16 @@
       <c r="R15" s="11"/>
       <c r="S15" s="11"/>
       <c r="T15" s="27"/>
-      <c r="U15" s="30"/>
-      <c r="V15" s="30"/>
-      <c r="W15" s="30"/>
+      <c r="U15" s="36"/>
+      <c r="V15" s="36"/>
+      <c r="W15" s="36"/>
     </row>
     <row r="16" spans="1:23" s="2" customFormat="1" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="36"/>
+      <c r="A16" s="42"/>
       <c r="B16" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="52">
+      <c r="C16" s="32">
         <v>3</v>
       </c>
       <c r="D16" s="28"/>
@@ -1568,7 +1568,7 @@
       <c r="F16" s="28"/>
       <c r="G16" s="28"/>
       <c r="H16" s="29"/>
-      <c r="I16" s="52">
+      <c r="I16" s="32">
         <v>0.3</v>
       </c>
       <c r="J16" s="28"/>
@@ -1576,7 +1576,7 @@
       <c r="L16" s="28"/>
       <c r="M16" s="28"/>
       <c r="N16" s="29"/>
-      <c r="O16" s="52">
+      <c r="O16" s="32">
         <v>0</v>
       </c>
       <c r="P16" s="28"/>
@@ -1584,16 +1584,16 @@
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
-      <c r="U16" s="30"/>
-      <c r="V16" s="30"/>
-      <c r="W16" s="30"/>
+      <c r="U16" s="36"/>
+      <c r="V16" s="36"/>
+      <c r="W16" s="36"/>
     </row>
     <row r="17" spans="1:23" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="33"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="53">
+      <c r="C17" s="33">
         <v>272</v>
       </c>
       <c r="D17" s="18"/>
@@ -1617,16 +1617,16 @@
       <c r="R17" s="18"/>
       <c r="S17" s="18"/>
       <c r="T17" s="20"/>
-      <c r="U17" s="30"/>
-      <c r="V17" s="30"/>
-      <c r="W17" s="30"/>
+      <c r="U17" s="36"/>
+      <c r="V17" s="36"/>
+      <c r="W17" s="36"/>
     </row>
     <row r="18" spans="1:23" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="30"/>
+      <c r="A18" s="36"/>
       <c r="B18" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="54">
+      <c r="C18" s="34">
         <v>216.97</v>
       </c>
       <c r="D18" s="16"/>
@@ -1635,7 +1635,7 @@
       <c r="G18" s="16"/>
       <c r="H18" s="16"/>
       <c r="I18" s="17">
-        <v>1.6887775412992805</v>
+        <v>1.5</v>
       </c>
       <c r="J18" s="16"/>
       <c r="K18" s="16"/>
@@ -1650,16 +1650,16 @@
       <c r="R18" s="16"/>
       <c r="S18" s="16"/>
       <c r="T18" s="21"/>
-      <c r="U18" s="30"/>
-      <c r="V18" s="30"/>
-      <c r="W18" s="30"/>
+      <c r="U18" s="36"/>
+      <c r="V18" s="36"/>
+      <c r="W18" s="36"/>
     </row>
     <row r="19" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="30"/>
+      <c r="A19" s="36"/>
       <c r="B19" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="55">
+      <c r="C19" s="35">
         <v>20.923076923076923</v>
       </c>
       <c r="D19" s="22"/>
@@ -1685,67 +1685,67 @@
       <c r="T19" s="24"/>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A20" s="30"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="31"/>
-      <c r="Q20" s="31"/>
-      <c r="R20" s="31"/>
-      <c r="S20" s="31"/>
+      <c r="A20" s="36"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="37"/>
+      <c r="M20" s="37"/>
+      <c r="N20" s="37"/>
+      <c r="O20" s="37"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="37"/>
+      <c r="R20" s="37"/>
+      <c r="S20" s="37"/>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A21" s="30"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="32"/>
-      <c r="O21" s="32"/>
-      <c r="P21" s="32"/>
-      <c r="Q21" s="32"/>
-      <c r="R21" s="32"/>
-      <c r="S21" s="32"/>
+      <c r="A21" s="36"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="38"/>
+      <c r="S21" s="38"/>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A22" s="30"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="32"/>
-      <c r="O22" s="32"/>
-      <c r="P22" s="32"/>
-      <c r="Q22" s="32"/>
-      <c r="R22" s="32"/>
-      <c r="S22" s="32"/>
+      <c r="A22" s="36"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="38"/>
+      <c r="P22" s="38"/>
+      <c r="Q22" s="38"/>
+      <c r="R22" s="38"/>
+      <c r="S22" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="12">
